--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmayores_a_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmayores_a_2024_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:02</t>
+    <t xml:space="preserve">2026-09-24 01:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -540,10 +540,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.36</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3">
@@ -554,10 +554,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4">
@@ -568,10 +568,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
@@ -582,10 +582,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
@@ -596,10 +596,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7">
@@ -764,10 +764,10 @@
         <v>23</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-0.66</v>
+        <v>-0.67</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19">
@@ -778,10 +778,10 @@
         <v>25</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20">
@@ -792,10 +792,10 @@
         <v>25</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21">
@@ -806,10 +806,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -820,10 +820,10 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.22</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         <v>0.06</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
